--- a/B1ControlExtensionBoardv232_2026-01-29.xlsx
+++ b/B1ControlExtensionBoardv232_2026-01-29.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFFCC"/>
+        <bgColor rgb="00CCFFCC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,38 +515,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FAILED CH1 (3.3VD): -0.0010735 (expected: 150.0 - 180.0); CH2 (5.0VD): -0.0011545 (expected: 2.0 - 2.1); CH3 (12V): -0.0011599 (expected: 2.0 - 2.1); CH4 (7V): -0.0011203 (expected: 2.0 - 2.1); CH6: -0.0012311 (expected: 2.1 - 2.2); CH7: -0.0010862 (expected: 1.0 - 1.1)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>-0.0010735</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-0.0011545</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-0.0011599</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-0.0011203</t>
+          <t>FAILED CH2 (5.0VD): -0.0001831 (expected: 2.0 - 2.1); CH3 (12V): -0.0004034 (expected: 2.0 - 2.1); CH4 (7V): -0.0002586 (expected: 2.0 - 2.1); CH6: -0.0003287 (expected: 2.1 - 2.2); CH7: -0.0003147 (expected: 1.0 - 1.1)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>3.3012368</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-0.0001831</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-0.0004034</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-0.0002586</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>-0.0012311</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>-0.0010862</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-0.0003287</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-0.0003147</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -549,7 +556,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-01-29 17:19:06</t>
+          <t>2026-01-29 18:03:36</t>
         </is>
       </c>
     </row>
@@ -564,33 +571,33 @@
           <t>FAILED CH1 (3.3VD): -0.0010274 (expected: 150.0 - 180.0); CH2 (5.0VD): -0.0011233 (expected: 2.0 - 2.1); CH3 (12V): -0.0011114 (expected: 2.0 - 2.1); CH4 (7V): -0.0011605 (expected: 2.0 - 2.1); CH6: -0.0010832 (expected: 2.1 - 2.2); CH7: -0.0010537 (expected: 1.0 - 1.1)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>-0.0010274</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>-0.0011233</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>-0.0011114</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-0.0011605</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>-0.0010832</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>-0.0010537</t>
         </is>

--- a/B1ControlExtensionBoardv232_2026-01-29.xlsx
+++ b/B1ControlExtensionBoardv232_2026-01-29.xlsx
@@ -17,13 +17,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -46,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,14 +59,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,185 +452,202 @@
   </sheetPr>
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="272" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TEST RESULT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>CH1 (3.3VD)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CH2 (5.0VD)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CH3 (12V)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CH4 (7V)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CH5</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CH6</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CH7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CH8</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CH9</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CH10</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>CH11</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>CH12</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Date/Time</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PSN000006047</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FAILED CH2 (5.0VD): -0.0001831 (expected: 2.0 - 2.1); CH3 (12V): -0.0004034 (expected: 2.0 - 2.1); CH4 (7V): -0.0002586 (expected: 2.0 - 2.1); CH6: -0.0003287 (expected: 2.1 - 2.2); CH7: -0.0003147 (expected: 1.0 - 1.1)</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>3.3012368</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-0.0001831</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>-0.0004034</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>-0.0002586</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-0.0003287</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-0.0003147</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-01-29 18:03:36</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FAILED CH2 (5.0VD): -0.0006273 (expected: 2.0 - 2.1); CH3 (12V): -0.0006922 (expected: 2.0 - 2.1); CH4 (7V): -0.0004386 (expected: 2.0 - 2.1); CH6: -0.0002427 (expected: 2.1 - 2.2); CH7: -0.0002427 (expected: 1.0 - 1.1)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>3.3016205</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>-0.0006273</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-0.0006922</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>-0.0004386</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>-0.0002427</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>-0.0002427</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29 18:20:18</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>PSN000002178</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>FAILED CH1 (3.3VD): -0.0010274 (expected: 150.0 - 180.0); CH2 (5.0VD): -0.0011233 (expected: 2.0 - 2.1); CH3 (12V): -0.0011114 (expected: 2.0 - 2.1); CH4 (7V): -0.0011605 (expected: 2.0 - 2.1); CH6: -0.0010832 (expected: 2.1 - 2.2); CH7: -0.0010537 (expected: 1.0 - 1.1)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>-0.0010274</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-0.0011233</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-0.0011114</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>-0.0011605</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>-0.0010832</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>-0.0010537</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2026-01-29 17:20:45</t>
         </is>

--- a/B1ControlExtensionBoardv232_2026-01-29.xlsx
+++ b/B1ControlExtensionBoardv232_2026-01-29.xlsx
@@ -555,38 +555,38 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FAILED CH2 (5.0VD): -0.0006273 (expected: 2.0 - 2.1); CH3 (12V): -0.0006922 (expected: 2.0 - 2.1); CH4 (7V): -0.0004386 (expected: 2.0 - 2.1); CH6: -0.0002427 (expected: 2.1 - 2.2); CH7: -0.0002427 (expected: 1.0 - 1.1)</t>
+          <t>FAILED CH2 (5.0VD): -0.0002437 (expected: 2.0 - 2.1); CH3 (12V): -0.0002765 (expected: 2.0 - 2.1); CH4 (7V): -0.0002750 (expected: 2.0 - 2.1); CH6: -0.0004657 (expected: 2.1 - 2.2); CH7: -0.0003592 (expected: 1.0 - 1.1)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3.3016205</t>
+          <t>3.3019297</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-0.0006273</t>
+          <t>-0.0002437</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-0.0006922</t>
+          <t>-0.0002765</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>-0.0004386</t>
+          <t>-0.0002750</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>-0.0002427</t>
+          <t>-0.0004657</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>-0.0002427</t>
+          <t>-0.0003592</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -596,7 +596,7 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29 18:20:18</t>
+          <t>2026-01-29 18:36:09</t>
         </is>
       </c>
     </row>
